--- a/analysis/hyperparameters.xlsx
+++ b/analysis/hyperparameters.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alexander Haeusser\Projects\forecast_engine\analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B26ED1D-9422-451A-8163-1B8BA5471CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C0FB1F-9CA7-4310-9DB4-7688BF90E2A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3782B9D1-AFB2-4CD4-A2A2-8F7C59906134}"/>
   </bookViews>
@@ -36,15 +36,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="9">
   <si>
     <t>alpha</t>
   </si>
   <si>
     <t>rho</t>
-  </si>
-  <si>
-    <t>n_states</t>
   </si>
   <si>
     <t>bic</t>
@@ -59,16 +56,13 @@
     <t>hqc</t>
   </si>
   <si>
-    <t>lambda_lower</t>
-  </si>
-  <si>
-    <t>lambda_upper</t>
-  </si>
-  <si>
     <t>inf_crit</t>
   </si>
   <si>
     <t>model</t>
+  </si>
+  <si>
+    <t>tau</t>
   </si>
 </sst>
 </file>
@@ -115,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -124,9 +118,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -463,19 +454,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93480AB0-1C0E-4372-99D0-814CCCBAA2A1}">
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
-    <col min="2" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="2" max="5" width="15.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -484,21 +475,15 @@
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1101</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3">
         <v>0.1</v>
@@ -506,22 +491,16 @@
       <c r="D2" s="2">
         <v>1</v>
       </c>
-      <c r="E2" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F2" s="1">
-        <v>2</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E2" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1102</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3">
         <v>0.2</v>
@@ -529,22 +508,16 @@
       <c r="D3" s="2">
         <v>1</v>
       </c>
-      <c r="E3" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F3" s="1">
-        <v>2</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E3" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1103</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3">
         <v>0.3</v>
@@ -552,22 +525,16 @@
       <c r="D4" s="2">
         <v>1</v>
       </c>
-      <c r="E4" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F4" s="1">
-        <v>2</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E4" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1104</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3">
         <v>0.4</v>
@@ -575,22 +542,16 @@
       <c r="D5" s="2">
         <v>1</v>
       </c>
-      <c r="E5" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F5" s="1">
-        <v>2</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E5" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1105</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="3">
         <v>0.5</v>
@@ -598,22 +559,16 @@
       <c r="D6" s="2">
         <v>1</v>
       </c>
-      <c r="E6" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F6" s="1">
-        <v>2</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E6" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1106</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="3">
         <v>0.6</v>
@@ -621,22 +576,16 @@
       <c r="D7" s="2">
         <v>1</v>
       </c>
-      <c r="E7" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F7" s="1">
-        <v>2</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E7" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1107</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" s="3">
         <v>0.7</v>
@@ -644,22 +593,16 @@
       <c r="D8" s="2">
         <v>1</v>
       </c>
-      <c r="E8" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F8" s="1">
-        <v>2</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E8" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1108</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" s="3">
         <v>0.8</v>
@@ -667,22 +610,16 @@
       <c r="D9" s="2">
         <v>1</v>
       </c>
-      <c r="E9" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F9" s="1">
-        <v>2</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E9" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1109</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" s="3">
         <v>0.9</v>
@@ -690,22 +627,16 @@
       <c r="D10" s="2">
         <v>1</v>
       </c>
-      <c r="E10" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F10" s="1">
-        <v>2</v>
-      </c>
-      <c r="G10" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E10" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1110</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
@@ -713,22 +644,16 @@
       <c r="D11" s="2">
         <v>1</v>
       </c>
-      <c r="E11" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F11" s="1">
-        <v>2</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E11" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1201</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" s="2">
         <v>1</v>
@@ -736,22 +661,16 @@
       <c r="D12" s="3">
         <v>0.5</v>
       </c>
-      <c r="E12" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F12" s="1">
-        <v>2</v>
-      </c>
-      <c r="G12" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E12" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1202</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" s="2">
         <v>1</v>
@@ -759,22 +678,16 @@
       <c r="D13" s="3">
         <v>0.6</v>
       </c>
-      <c r="E13" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F13" s="1">
-        <v>2</v>
-      </c>
-      <c r="G13" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E13" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>1203</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" s="2">
         <v>1</v>
@@ -782,22 +695,16 @@
       <c r="D14" s="3">
         <v>0.7</v>
       </c>
-      <c r="E14" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F14" s="1">
-        <v>2</v>
-      </c>
-      <c r="G14" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E14" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1204</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" s="2">
         <v>1</v>
@@ -805,22 +712,16 @@
       <c r="D15" s="3">
         <v>0.8</v>
       </c>
-      <c r="E15" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F15" s="1">
-        <v>2</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E15" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1205</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" s="2">
         <v>1</v>
@@ -828,22 +729,16 @@
       <c r="D16" s="3">
         <v>0.9</v>
       </c>
-      <c r="E16" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F16" s="1">
-        <v>2</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E16" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1206</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
@@ -851,22 +746,16 @@
       <c r="D17" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E17" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F17" s="1">
-        <v>2</v>
-      </c>
-      <c r="G17" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E17" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>1207</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" s="2">
         <v>1</v>
@@ -874,22 +763,16 @@
       <c r="D18" s="3">
         <v>1</v>
       </c>
-      <c r="E18" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F18" s="1">
-        <v>2</v>
-      </c>
-      <c r="G18" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E18" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>1208</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
@@ -897,22 +780,16 @@
       <c r="D19" s="3">
         <v>1.2</v>
       </c>
-      <c r="E19" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F19" s="1">
-        <v>2</v>
-      </c>
-      <c r="G19" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E19" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>1209</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" s="2">
         <v>1</v>
@@ -920,22 +797,16 @@
       <c r="D20" s="3">
         <v>1.3</v>
       </c>
-      <c r="E20" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F20" s="1">
-        <v>2</v>
-      </c>
-      <c r="G20" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E20" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>1210</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21" s="2">
         <v>1</v>
@@ -943,22 +814,16 @@
       <c r="D21" s="3">
         <v>1.4</v>
       </c>
-      <c r="E21" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F21" s="1">
-        <v>2</v>
-      </c>
-      <c r="G21" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E21" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1211</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" s="2">
         <v>1</v>
@@ -966,22 +831,16 @@
       <c r="D22" s="3">
         <v>1.5</v>
       </c>
-      <c r="E22" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F22" s="1">
-        <v>2</v>
-      </c>
-      <c r="G22" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E22" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>1301</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23" s="2">
         <v>1</v>
@@ -989,22 +848,16 @@
       <c r="D23" s="2">
         <v>1</v>
       </c>
-      <c r="E23" s="4">
-        <v>8.0000000000000002E-8</v>
-      </c>
-      <c r="F23" s="4">
-        <v>8</v>
-      </c>
-      <c r="G23" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E23" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>1302</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C24" s="2">
         <v>1</v>
@@ -1012,22 +865,16 @@
       <c r="D24" s="2">
         <v>1</v>
       </c>
-      <c r="E24" s="4">
-        <v>8.0000000000000002E-8</v>
-      </c>
-      <c r="F24" s="4">
-        <v>2</v>
-      </c>
-      <c r="G24" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E24" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>1303</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -1035,22 +882,16 @@
       <c r="D25" s="2">
         <v>1</v>
       </c>
-      <c r="E25" s="4">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F25" s="4">
-        <v>8</v>
-      </c>
-      <c r="G25" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E25" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>1401</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C26" s="2">
         <v>1</v>
@@ -1058,22 +899,16 @@
       <c r="D26" s="2">
         <v>1</v>
       </c>
-      <c r="E26" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F26" s="1">
-        <v>2</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="E26" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>1402</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" s="2">
         <v>1</v>
@@ -1081,22 +916,16 @@
       <c r="D27" s="2">
         <v>1</v>
       </c>
-      <c r="E27" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F27" s="1">
-        <v>2</v>
-      </c>
-      <c r="G27" s="3">
+      <c r="E27" s="3">
         <v>0.6</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>1403</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28" s="2">
         <v>1</v>
@@ -1104,22 +933,16 @@
       <c r="D28" s="2">
         <v>1</v>
       </c>
-      <c r="E28" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F28" s="1">
-        <v>2</v>
-      </c>
-      <c r="G28" s="3">
+      <c r="E28" s="3">
         <v>0.8</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>1404</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" s="2">
         <v>1</v>
@@ -1127,22 +950,16 @@
       <c r="D29" s="2">
         <v>1</v>
       </c>
-      <c r="E29" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F29" s="1">
-        <v>2</v>
-      </c>
-      <c r="G29" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E29" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2101</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C30" s="3">
         <v>0.1</v>
@@ -1150,22 +967,16 @@
       <c r="D30" s="2">
         <v>1</v>
       </c>
-      <c r="E30" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F30" s="1">
-        <v>2</v>
-      </c>
-      <c r="G30" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E30" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2102</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C31" s="3">
         <v>0.2</v>
@@ -1173,22 +984,16 @@
       <c r="D31" s="2">
         <v>1</v>
       </c>
-      <c r="E31" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F31" s="1">
-        <v>2</v>
-      </c>
-      <c r="G31" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E31" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2103</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C32" s="3">
         <v>0.3</v>
@@ -1196,22 +1001,16 @@
       <c r="D32" s="2">
         <v>1</v>
       </c>
-      <c r="E32" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F32" s="1">
-        <v>2</v>
-      </c>
-      <c r="G32" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E32" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>2104</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C33" s="3">
         <v>0.4</v>
@@ -1219,22 +1018,16 @@
       <c r="D33" s="2">
         <v>1</v>
       </c>
-      <c r="E33" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F33" s="1">
-        <v>2</v>
-      </c>
-      <c r="G33" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E33" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2105</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C34" s="3">
         <v>0.5</v>
@@ -1242,22 +1035,16 @@
       <c r="D34" s="2">
         <v>1</v>
       </c>
-      <c r="E34" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F34" s="1">
-        <v>2</v>
-      </c>
-      <c r="G34" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E34" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2106</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C35" s="3">
         <v>0.6</v>
@@ -1265,22 +1052,16 @@
       <c r="D35" s="2">
         <v>1</v>
       </c>
-      <c r="E35" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F35" s="1">
-        <v>2</v>
-      </c>
-      <c r="G35" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E35" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2107</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C36" s="3">
         <v>0.7</v>
@@ -1288,22 +1069,16 @@
       <c r="D36" s="2">
         <v>1</v>
       </c>
-      <c r="E36" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F36" s="1">
-        <v>2</v>
-      </c>
-      <c r="G36" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E36" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2108</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C37" s="3">
         <v>0.8</v>
@@ -1311,22 +1086,16 @@
       <c r="D37" s="2">
         <v>1</v>
       </c>
-      <c r="E37" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F37" s="1">
-        <v>2</v>
-      </c>
-      <c r="G37" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E37" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2109</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C38" s="3">
         <v>0.9</v>
@@ -1334,22 +1103,16 @@
       <c r="D38" s="2">
         <v>1</v>
       </c>
-      <c r="E38" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F38" s="1">
-        <v>2</v>
-      </c>
-      <c r="G38" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E38" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2110</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C39" s="3">
         <v>1</v>
@@ -1357,22 +1120,16 @@
       <c r="D39" s="2">
         <v>1</v>
       </c>
-      <c r="E39" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F39" s="1">
-        <v>2</v>
-      </c>
-      <c r="G39" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E39" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>2201</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C40" s="2">
         <v>1</v>
@@ -1380,22 +1137,16 @@
       <c r="D40" s="3">
         <v>0.5</v>
       </c>
-      <c r="E40" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F40" s="1">
-        <v>2</v>
-      </c>
-      <c r="G40" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E40" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>2202</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C41" s="2">
         <v>1</v>
@@ -1403,22 +1154,16 @@
       <c r="D41" s="3">
         <v>0.6</v>
       </c>
-      <c r="E41" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F41" s="1">
-        <v>2</v>
-      </c>
-      <c r="G41" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E41" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>2203</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C42" s="2">
         <v>1</v>
@@ -1426,22 +1171,16 @@
       <c r="D42" s="3">
         <v>0.7</v>
       </c>
-      <c r="E42" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F42" s="1">
-        <v>2</v>
-      </c>
-      <c r="G42" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E42" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2204</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C43" s="2">
         <v>1</v>
@@ -1449,22 +1188,16 @@
       <c r="D43" s="3">
         <v>0.8</v>
       </c>
-      <c r="E43" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F43" s="1">
-        <v>2</v>
-      </c>
-      <c r="G43" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E43" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>2205</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C44" s="2">
         <v>1</v>
@@ -1472,22 +1205,16 @@
       <c r="D44" s="3">
         <v>0.9</v>
       </c>
-      <c r="E44" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F44" s="1">
-        <v>2</v>
-      </c>
-      <c r="G44" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E44" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>2206</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C45" s="2">
         <v>1</v>
@@ -1495,22 +1222,16 @@
       <c r="D45" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E45" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F45" s="1">
-        <v>2</v>
-      </c>
-      <c r="G45" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E45" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>2207</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C46" s="2">
         <v>1</v>
@@ -1518,22 +1239,16 @@
       <c r="D46" s="3">
         <v>1</v>
       </c>
-      <c r="E46" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F46" s="1">
-        <v>2</v>
-      </c>
-      <c r="G46" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E46" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>2208</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C47" s="2">
         <v>1</v>
@@ -1541,22 +1256,16 @@
       <c r="D47" s="3">
         <v>1.2</v>
       </c>
-      <c r="E47" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F47" s="1">
-        <v>2</v>
-      </c>
-      <c r="G47" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E47" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>2209</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C48" s="2">
         <v>1</v>
@@ -1564,22 +1273,16 @@
       <c r="D48" s="3">
         <v>1.3</v>
       </c>
-      <c r="E48" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F48" s="1">
-        <v>2</v>
-      </c>
-      <c r="G48" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E48" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>2210</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C49" s="2">
         <v>1</v>
@@ -1587,22 +1290,16 @@
       <c r="D49" s="3">
         <v>1.4</v>
       </c>
-      <c r="E49" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F49" s="1">
-        <v>2</v>
-      </c>
-      <c r="G49" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E49" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>2211</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C50" s="2">
         <v>1</v>
@@ -1610,22 +1307,16 @@
       <c r="D50" s="3">
         <v>1.5</v>
       </c>
-      <c r="E50" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F50" s="1">
-        <v>2</v>
-      </c>
-      <c r="G50" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E50" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>2301</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C51" s="2">
         <v>1</v>
@@ -1633,22 +1324,16 @@
       <c r="D51" s="2">
         <v>1</v>
       </c>
-      <c r="E51" s="4">
-        <v>8.0000000000000002E-8</v>
-      </c>
-      <c r="F51" s="4">
-        <v>8</v>
-      </c>
-      <c r="G51" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E51" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>2302</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C52" s="2">
         <v>1</v>
@@ -1656,22 +1341,16 @@
       <c r="D52" s="2">
         <v>1</v>
       </c>
-      <c r="E52" s="4">
-        <v>8.0000000000000002E-8</v>
-      </c>
-      <c r="F52" s="4">
-        <v>2</v>
-      </c>
-      <c r="G52" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E52" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>2303</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C53" s="2">
         <v>1</v>
@@ -1679,22 +1358,16 @@
       <c r="D53" s="2">
         <v>1</v>
       </c>
-      <c r="E53" s="4">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F53" s="4">
-        <v>8</v>
-      </c>
-      <c r="G53" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E53" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>2401</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C54" s="2">
         <v>1</v>
@@ -1702,22 +1375,16 @@
       <c r="D54" s="2">
         <v>1</v>
       </c>
-      <c r="E54" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F54" s="1">
-        <v>2</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="E54" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>2402</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C55" s="2">
         <v>1</v>
@@ -1725,22 +1392,16 @@
       <c r="D55" s="2">
         <v>1</v>
       </c>
-      <c r="E55" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F55" s="1">
-        <v>2</v>
-      </c>
-      <c r="G55" s="3">
+      <c r="E55" s="3">
         <v>0.6</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>2403</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C56" s="2">
         <v>1</v>
@@ -1748,22 +1409,16 @@
       <c r="D56" s="2">
         <v>1</v>
       </c>
-      <c r="E56" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F56" s="1">
-        <v>2</v>
-      </c>
-      <c r="G56" s="3">
+      <c r="E56" s="3">
         <v>0.8</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>2404</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C57" s="2">
         <v>1</v>
@@ -1771,22 +1426,16 @@
       <c r="D57" s="2">
         <v>1</v>
       </c>
-      <c r="E57" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F57" s="1">
-        <v>2</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E57" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>3101</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C58" s="3">
         <v>0.1</v>
@@ -1794,22 +1443,16 @@
       <c r="D58" s="2">
         <v>1</v>
       </c>
-      <c r="E58" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F58" s="1">
-        <v>2</v>
-      </c>
-      <c r="G58" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E58" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>3102</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C59" s="3">
         <v>0.2</v>
@@ -1817,22 +1460,16 @@
       <c r="D59" s="2">
         <v>1</v>
       </c>
-      <c r="E59" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F59" s="1">
-        <v>2</v>
-      </c>
-      <c r="G59" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E59" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>3103</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C60" s="3">
         <v>0.3</v>
@@ -1840,22 +1477,16 @@
       <c r="D60" s="2">
         <v>1</v>
       </c>
-      <c r="E60" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F60" s="1">
-        <v>2</v>
-      </c>
-      <c r="G60" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E60" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>3104</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C61" s="3">
         <v>0.4</v>
@@ -1863,22 +1494,16 @@
       <c r="D61" s="2">
         <v>1</v>
       </c>
-      <c r="E61" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F61" s="1">
-        <v>2</v>
-      </c>
-      <c r="G61" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E61" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>3105</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C62" s="3">
         <v>0.5</v>
@@ -1886,22 +1511,16 @@
       <c r="D62" s="2">
         <v>1</v>
       </c>
-      <c r="E62" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F62" s="1">
-        <v>2</v>
-      </c>
-      <c r="G62" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E62" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>3106</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C63" s="3">
         <v>0.6</v>
@@ -1909,22 +1528,16 @@
       <c r="D63" s="2">
         <v>1</v>
       </c>
-      <c r="E63" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F63" s="1">
-        <v>2</v>
-      </c>
-      <c r="G63" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E63" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>3107</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C64" s="3">
         <v>0.7</v>
@@ -1932,22 +1545,16 @@
       <c r="D64" s="2">
         <v>1</v>
       </c>
-      <c r="E64" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F64" s="1">
-        <v>2</v>
-      </c>
-      <c r="G64" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E64" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>3108</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C65" s="3">
         <v>0.8</v>
@@ -1955,22 +1562,16 @@
       <c r="D65" s="2">
         <v>1</v>
       </c>
-      <c r="E65" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F65" s="1">
-        <v>2</v>
-      </c>
-      <c r="G65" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E65" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>3109</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C66" s="3">
         <v>0.9</v>
@@ -1978,22 +1579,16 @@
       <c r="D66" s="2">
         <v>1</v>
       </c>
-      <c r="E66" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F66" s="1">
-        <v>2</v>
-      </c>
-      <c r="G66" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E66" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>3110</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C67" s="3">
         <v>1</v>
@@ -2001,22 +1596,16 @@
       <c r="D67" s="2">
         <v>1</v>
       </c>
-      <c r="E67" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F67" s="1">
-        <v>2</v>
-      </c>
-      <c r="G67" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E67" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>3201</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C68" s="2">
         <v>1</v>
@@ -2024,22 +1613,16 @@
       <c r="D68" s="3">
         <v>0.5</v>
       </c>
-      <c r="E68" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F68" s="1">
-        <v>2</v>
-      </c>
-      <c r="G68" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E68" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>3202</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C69" s="2">
         <v>1</v>
@@ -2047,22 +1630,16 @@
       <c r="D69" s="3">
         <v>0.6</v>
       </c>
-      <c r="E69" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F69" s="1">
-        <v>2</v>
-      </c>
-      <c r="G69" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E69" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>3203</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C70" s="2">
         <v>1</v>
@@ -2070,22 +1647,16 @@
       <c r="D70" s="3">
         <v>0.7</v>
       </c>
-      <c r="E70" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F70" s="1">
-        <v>2</v>
-      </c>
-      <c r="G70" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E70" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>3204</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C71" s="2">
         <v>1</v>
@@ -2093,22 +1664,16 @@
       <c r="D71" s="3">
         <v>0.8</v>
       </c>
-      <c r="E71" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F71" s="1">
-        <v>2</v>
-      </c>
-      <c r="G71" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E71" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>3205</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C72" s="2">
         <v>1</v>
@@ -2116,22 +1681,16 @@
       <c r="D72" s="3">
         <v>0.9</v>
       </c>
-      <c r="E72" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F72" s="1">
-        <v>2</v>
-      </c>
-      <c r="G72" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E72" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>3206</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C73" s="2">
         <v>1</v>
@@ -2139,22 +1698,16 @@
       <c r="D73" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E73" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F73" s="1">
-        <v>2</v>
-      </c>
-      <c r="G73" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E73" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>3207</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C74" s="2">
         <v>1</v>
@@ -2162,22 +1715,16 @@
       <c r="D74" s="3">
         <v>1</v>
       </c>
-      <c r="E74" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F74" s="1">
-        <v>2</v>
-      </c>
-      <c r="G74" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E74" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>3208</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C75" s="2">
         <v>1</v>
@@ -2185,22 +1732,16 @@
       <c r="D75" s="3">
         <v>1.2</v>
       </c>
-      <c r="E75" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F75" s="1">
-        <v>2</v>
-      </c>
-      <c r="G75" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E75" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>3209</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C76" s="2">
         <v>1</v>
@@ -2208,22 +1749,16 @@
       <c r="D76" s="3">
         <v>1.3</v>
       </c>
-      <c r="E76" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F76" s="1">
-        <v>2</v>
-      </c>
-      <c r="G76" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E76" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>3210</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C77" s="2">
         <v>1</v>
@@ -2231,22 +1766,16 @@
       <c r="D77" s="3">
         <v>1.4</v>
       </c>
-      <c r="E77" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F77" s="1">
-        <v>2</v>
-      </c>
-      <c r="G77" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E77" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>3211</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
@@ -2254,22 +1783,16 @@
       <c r="D78" s="3">
         <v>1.5</v>
       </c>
-      <c r="E78" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F78" s="1">
-        <v>2</v>
-      </c>
-      <c r="G78" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E78" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>3301</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -2277,22 +1800,16 @@
       <c r="D79" s="2">
         <v>1</v>
       </c>
-      <c r="E79" s="4">
-        <v>8.0000000000000002E-8</v>
-      </c>
-      <c r="F79" s="4">
-        <v>8</v>
-      </c>
-      <c r="G79" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E79" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>3302</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
@@ -2300,22 +1817,16 @@
       <c r="D80" s="2">
         <v>1</v>
       </c>
-      <c r="E80" s="4">
-        <v>8.0000000000000002E-8</v>
-      </c>
-      <c r="F80" s="4">
-        <v>2</v>
-      </c>
-      <c r="G80" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E80" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>3303</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
@@ -2323,22 +1834,16 @@
       <c r="D81" s="2">
         <v>1</v>
       </c>
-      <c r="E81" s="4">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F81" s="4">
-        <v>8</v>
-      </c>
-      <c r="G81" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E81" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>3401</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C82" s="2">
         <v>1</v>
@@ -2346,22 +1851,16 @@
       <c r="D82" s="2">
         <v>1</v>
       </c>
-      <c r="E82" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F82" s="1">
-        <v>2</v>
-      </c>
-      <c r="G82" s="3">
+      <c r="E82" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>3402</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C83" s="2">
         <v>1</v>
@@ -2369,22 +1868,16 @@
       <c r="D83" s="2">
         <v>1</v>
       </c>
-      <c r="E83" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F83" s="1">
-        <v>2</v>
-      </c>
-      <c r="G83" s="3">
+      <c r="E83" s="3">
         <v>0.6</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>3403</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C84" s="2">
         <v>1</v>
@@ -2392,22 +1885,16 @@
       <c r="D84" s="2">
         <v>1</v>
       </c>
-      <c r="E84" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F84" s="1">
-        <v>2</v>
-      </c>
-      <c r="G84" s="3">
+      <c r="E84" s="3">
         <v>0.8</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>3404</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C85" s="2">
         <v>1</v>
@@ -2415,22 +1902,16 @@
       <c r="D85" s="2">
         <v>1</v>
       </c>
-      <c r="E85" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F85" s="1">
-        <v>2</v>
-      </c>
-      <c r="G85" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E85" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>4101</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C86" s="3">
         <v>0.1</v>
@@ -2438,22 +1919,16 @@
       <c r="D86" s="2">
         <v>1</v>
       </c>
-      <c r="E86" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F86" s="1">
-        <v>2</v>
-      </c>
-      <c r="G86" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E86" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>4102</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C87" s="3">
         <v>0.2</v>
@@ -2461,22 +1936,16 @@
       <c r="D87" s="2">
         <v>1</v>
       </c>
-      <c r="E87" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F87" s="1">
-        <v>2</v>
-      </c>
-      <c r="G87" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E87" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>4103</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C88" s="3">
         <v>0.3</v>
@@ -2484,22 +1953,16 @@
       <c r="D88" s="2">
         <v>1</v>
       </c>
-      <c r="E88" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F88" s="1">
-        <v>2</v>
-      </c>
-      <c r="G88" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E88" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>4104</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C89" s="3">
         <v>0.4</v>
@@ -2507,22 +1970,16 @@
       <c r="D89" s="2">
         <v>1</v>
       </c>
-      <c r="E89" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F89" s="1">
-        <v>2</v>
-      </c>
-      <c r="G89" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E89" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>4105</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C90" s="3">
         <v>0.5</v>
@@ -2530,22 +1987,16 @@
       <c r="D90" s="2">
         <v>1</v>
       </c>
-      <c r="E90" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F90" s="1">
-        <v>2</v>
-      </c>
-      <c r="G90" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E90" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>4106</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C91" s="3">
         <v>0.6</v>
@@ -2553,22 +2004,16 @@
       <c r="D91" s="2">
         <v>1</v>
       </c>
-      <c r="E91" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F91" s="1">
-        <v>2</v>
-      </c>
-      <c r="G91" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E91" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>4107</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C92" s="3">
         <v>0.7</v>
@@ -2576,22 +2021,16 @@
       <c r="D92" s="2">
         <v>1</v>
       </c>
-      <c r="E92" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F92" s="1">
-        <v>2</v>
-      </c>
-      <c r="G92" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E92" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>4108</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C93" s="3">
         <v>0.8</v>
@@ -2599,22 +2038,16 @@
       <c r="D93" s="2">
         <v>1</v>
       </c>
-      <c r="E93" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F93" s="1">
-        <v>2</v>
-      </c>
-      <c r="G93" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E93" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>4109</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C94" s="3">
         <v>0.9</v>
@@ -2622,22 +2055,16 @@
       <c r="D94" s="2">
         <v>1</v>
       </c>
-      <c r="E94" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F94" s="1">
-        <v>2</v>
-      </c>
-      <c r="G94" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E94" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>4110</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C95" s="3">
         <v>1</v>
@@ -2645,22 +2072,16 @@
       <c r="D95" s="2">
         <v>1</v>
       </c>
-      <c r="E95" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F95" s="1">
-        <v>2</v>
-      </c>
-      <c r="G95" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E95" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>4201</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C96" s="2">
         <v>1</v>
@@ -2668,22 +2089,16 @@
       <c r="D96" s="3">
         <v>0.5</v>
       </c>
-      <c r="E96" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F96" s="1">
-        <v>2</v>
-      </c>
-      <c r="G96" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E96" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>4202</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C97" s="2">
         <v>1</v>
@@ -2691,22 +2106,16 @@
       <c r="D97" s="3">
         <v>0.6</v>
       </c>
-      <c r="E97" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F97" s="1">
-        <v>2</v>
-      </c>
-      <c r="G97" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E97" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>4203</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C98" s="2">
         <v>1</v>
@@ -2714,22 +2123,16 @@
       <c r="D98" s="3">
         <v>0.7</v>
       </c>
-      <c r="E98" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F98" s="1">
-        <v>2</v>
-      </c>
-      <c r="G98" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E98" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>4204</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C99" s="2">
         <v>1</v>
@@ -2737,22 +2140,16 @@
       <c r="D99" s="3">
         <v>0.8</v>
       </c>
-      <c r="E99" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F99" s="1">
-        <v>2</v>
-      </c>
-      <c r="G99" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E99" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>4205</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
@@ -2760,22 +2157,16 @@
       <c r="D100" s="3">
         <v>0.9</v>
       </c>
-      <c r="E100" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F100" s="1">
-        <v>2</v>
-      </c>
-      <c r="G100" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E100" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>4206</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C101" s="2">
         <v>1</v>
@@ -2783,22 +2174,16 @@
       <c r="D101" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="E101" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F101" s="1">
-        <v>2</v>
-      </c>
-      <c r="G101" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E101" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>4207</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
@@ -2806,22 +2191,16 @@
       <c r="D102" s="3">
         <v>1</v>
       </c>
-      <c r="E102" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F102" s="1">
-        <v>2</v>
-      </c>
-      <c r="G102" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E102" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>4208</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C103" s="2">
         <v>1</v>
@@ -2829,22 +2208,16 @@
       <c r="D103" s="3">
         <v>1.2</v>
       </c>
-      <c r="E103" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F103" s="1">
-        <v>2</v>
-      </c>
-      <c r="G103" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E103" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>4209</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C104" s="2">
         <v>1</v>
@@ -2852,22 +2225,16 @@
       <c r="D104" s="3">
         <v>1.3</v>
       </c>
-      <c r="E104" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F104" s="1">
-        <v>2</v>
-      </c>
-      <c r="G104" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E104" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>4210</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C105" s="2">
         <v>1</v>
@@ -2875,22 +2242,16 @@
       <c r="D105" s="3">
         <v>1.4</v>
       </c>
-      <c r="E105" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F105" s="1">
-        <v>2</v>
-      </c>
-      <c r="G105" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E105" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>4211</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C106" s="2">
         <v>1</v>
@@ -2898,22 +2259,16 @@
       <c r="D106" s="3">
         <v>1.5</v>
       </c>
-      <c r="E106" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F106" s="1">
-        <v>2</v>
-      </c>
-      <c r="G106" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E106" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>4301</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C107" s="2">
         <v>1</v>
@@ -2921,22 +2276,16 @@
       <c r="D107" s="2">
         <v>1</v>
       </c>
-      <c r="E107" s="4">
-        <v>8.0000000000000002E-8</v>
-      </c>
-      <c r="F107" s="4">
-        <v>8</v>
-      </c>
-      <c r="G107" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E107" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>4302</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C108" s="2">
         <v>1</v>
@@ -2944,22 +2293,16 @@
       <c r="D108" s="2">
         <v>1</v>
       </c>
-      <c r="E108" s="4">
-        <v>8.0000000000000002E-8</v>
-      </c>
-      <c r="F108" s="4">
-        <v>2</v>
-      </c>
-      <c r="G108" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E108" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>4303</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C109" s="2">
         <v>1</v>
@@ -2967,22 +2310,16 @@
       <c r="D109" s="2">
         <v>1</v>
       </c>
-      <c r="E109" s="4">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F109" s="4">
-        <v>8</v>
-      </c>
-      <c r="G109" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E109" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>4401</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C110" s="2">
         <v>1</v>
@@ -2990,22 +2327,16 @@
       <c r="D110" s="2">
         <v>1</v>
       </c>
-      <c r="E110" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F110" s="1">
-        <v>2</v>
-      </c>
-      <c r="G110" s="3">
+      <c r="E110" s="3">
         <v>0.2</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>4402</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C111" s="2">
         <v>1</v>
@@ -3013,22 +2344,16 @@
       <c r="D111" s="2">
         <v>1</v>
       </c>
-      <c r="E111" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F111" s="1">
-        <v>2</v>
-      </c>
-      <c r="G111" s="3">
+      <c r="E111" s="3">
         <v>0.6</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>4403</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C112" s="2">
         <v>1</v>
@@ -3036,22 +2361,16 @@
       <c r="D112" s="2">
         <v>1</v>
       </c>
-      <c r="E112" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F112" s="1">
-        <v>2</v>
-      </c>
-      <c r="G112" s="3">
+      <c r="E112" s="3">
         <v>0.8</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>4404</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C113" s="2">
         <v>1</v>
@@ -3059,13 +2378,7 @@
       <c r="D113" s="2">
         <v>1</v>
       </c>
-      <c r="E113" s="1">
-        <v>4.0000000000000002E-4</v>
-      </c>
-      <c r="F113" s="1">
-        <v>2</v>
-      </c>
-      <c r="G113" s="3">
+      <c r="E113" s="3">
         <v>1</v>
       </c>
     </row>
